--- a/Libraries/Vehicle/Driveline/Axle2/sm_car_data_Driveline_Axle2_A1_A1Diff.xlsx
+++ b/Libraries/Vehicle/Driveline/Axle2/sm_car_data_Driveline_Axle2_A1_A1Diff.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt\Libraries\Vehicle\Driveline\Axle2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Driveline\Axle2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467EACC7-790A-455B-9679-F57AD337C6C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2C4665-DEE8-4980-A9FA-149FBF91B51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2568" yWindow="540" windowWidth="17280" windowHeight="10152" xr2:uid="{63F140F1-6588-40C2-A567-D265B347A840}"/>
+    <workbookView xWindow="29715" yWindow="2880" windowWidth="21600" windowHeight="11295" xr2:uid="{63F140F1-6588-40C2-A567-D265B347A840}"/>
   </bookViews>
   <sheets>
-    <sheet name="FuelCell1Motor" sheetId="1" r:id="rId1"/>
+    <sheet name="default" sheetId="2" r:id="rId1"/>
+    <sheet name="FuelCell1Motor" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>Units</t>
   </si>
@@ -88,6 +89,9 @@
   </si>
   <si>
     <t>A1_A1Diff</t>
+  </si>
+  <si>
+    <t>Axle2_A1_A1Diff_default</t>
   </si>
 </sst>
 </file>
@@ -152,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -161,44 +165,76 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -269,9 +305,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -309,7 +345,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -415,7 +451,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -557,30 +593,30 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D889ED8C-EB67-4A21-83A1-094649CAB3EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD456F30-F5BF-411E-9591-76ACD294DE1D}">
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" style="18" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="8" width="10" customWidth="1"/>
-    <col min="9" max="15" width="6.6640625" customWidth="1"/>
+    <col min="9" max="15" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -600,7 +636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -613,25 +649,160 @@
       <c r="H2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-    </row>
-    <row r="3" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="E5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="H6" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="H7" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="H8" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A4 C4 A6">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:B5">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:C8">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D889ED8C-EB67-4A21-83A1-094649CAB3EA}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="15" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -645,401 +816,118 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-      <c r="N4"/>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4"/>
-      <c r="R4"/>
-      <c r="S4"/>
-      <c r="T4"/>
-      <c r="U4"/>
-      <c r="V4"/>
-      <c r="W4"/>
-      <c r="X4"/>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4"/>
-    </row>
-    <row r="5" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16">
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="14">
         <v>5</v>
       </c>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
-      <c r="N5"/>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-      <c r="R5"/>
-      <c r="S5"/>
-      <c r="T5"/>
-      <c r="U5"/>
-      <c r="V5"/>
-      <c r="W5"/>
-      <c r="X5"/>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5"/>
-    </row>
-    <row r="6" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-      <c r="R6"/>
-      <c r="S6"/>
-      <c r="T6"/>
-      <c r="U6"/>
-      <c r="V6"/>
-      <c r="W6"/>
-      <c r="X6"/>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6"/>
-    </row>
-    <row r="7" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
-      <c r="H10" s="17"/>
-    </row>
-    <row r="11" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-    </row>
-    <row r="14" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-    </row>
-    <row r="15" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-    </row>
-    <row r="16" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-    </row>
-    <row r="17" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-    </row>
-    <row r="18" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
-      <c r="H18"/>
-    </row>
-    <row r="19" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-    </row>
-    <row r="20" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-    </row>
-    <row r="21" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-    </row>
-    <row r="22" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
-    </row>
-    <row r="23" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="18"/>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-    </row>
-    <row r="24" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24"/>
-      <c r="M24"/>
-      <c r="N24"/>
-      <c r="O24"/>
-      <c r="P24"/>
-      <c r="Q24"/>
-      <c r="R24"/>
-      <c r="S24"/>
-      <c r="T24"/>
-    </row>
-    <row r="25" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25"/>
-      <c r="M25"/>
-      <c r="N25"/>
-      <c r="O25"/>
-      <c r="P25"/>
-      <c r="Q25"/>
-      <c r="R25"/>
-      <c r="S25"/>
-      <c r="T25"/>
-    </row>
-    <row r="26" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="18"/>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26"/>
-      <c r="P26"/>
-      <c r="Q26"/>
-      <c r="R26"/>
-      <c r="S26"/>
-      <c r="T26"/>
-    </row>
-    <row r="27" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="18"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
-      <c r="I27"/>
-      <c r="J27"/>
-      <c r="K27"/>
-      <c r="L27"/>
-      <c r="M27"/>
-      <c r="N27"/>
-      <c r="O27"/>
-      <c r="P27"/>
-      <c r="Q27"/>
-      <c r="R27"/>
-      <c r="S27"/>
-      <c r="T27"/>
-    </row>
-    <row r="28" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="18"/>
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
-      <c r="I28"/>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
-      <c r="M28"/>
-      <c r="N28"/>
-      <c r="O28"/>
-      <c r="P28"/>
-      <c r="Q28"/>
-      <c r="R28"/>
-      <c r="S28"/>
-      <c r="T28"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H12" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D10:D11 B12 A6 C4 A4 B7:C8">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:B11">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+  <conditionalFormatting sqref="A4 C4 A6 D10:D11">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:B5">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B9">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11:B11">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:C6">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:B5">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B9">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A11:B11">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:B12">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:C8">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
